--- a/documentación/PRSC/Dailys.xlsx
+++ b/documentación/PRSC/Dailys.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="68">
   <si>
     <t xml:space="preserve">Daily</t>
   </si>
@@ -170,6 +170,60 @@
   </si>
   <si>
     <t xml:space="preserve">Elección de arquitectura del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creacion del SQL de la base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantallas avance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presupuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagrama de contexto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFD 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFD 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantallas AMB usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creacion del backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creacion de querys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing de la pagina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing de la recuperar contraseña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantallas de favoritos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy de proyecto en render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subir el codigo a github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglos en render de enviroment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregar brevo el render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conexion supabe al proyecto</t>
   </si>
 </sst>
 </file>
@@ -179,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -235,12 +289,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -318,7 +367,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -364,10 +413,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -451,37 +496,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -621,10 +666,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:GC195"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.38"/>
   </cols>
@@ -880,7 +925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
@@ -903,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
         <v>14</v>
       </c>
@@ -972,7 +1017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
@@ -995,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
@@ -1018,7 +1063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
@@ -1041,7 +1086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
@@ -1064,7 +1109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
@@ -1087,7 +1132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
@@ -1110,7 +1155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
@@ -1133,7 +1178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
         <v>14</v>
       </c>
@@ -1156,7 +1201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
         <v>14</v>
       </c>
@@ -1179,7 +1224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
         <v>14</v>
       </c>
@@ -1202,7 +1247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
@@ -1248,7 +1293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
         <v>14</v>
       </c>
@@ -1317,7 +1362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
         <v>14</v>
       </c>
@@ -1382,7 +1427,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1405,7 +1450,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1428,7 +1473,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1451,7 +1496,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1474,7 +1519,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1497,196 +1542,400 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="J34" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
+      <c r="J35" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="J38" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
+      <c r="J39" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
+      <c r="J40" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>59</v>
+      </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
+      <c r="J42" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
+      <c r="J43" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
+      <c r="J44" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
+      <c r="J45" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
+      <c r="J46" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
+      <c r="J47" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="B48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
+      <c r="J48" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="B49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
+      <c r="J49" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="8"/>

--- a/documentación/PRSC/Dailys.xlsx
+++ b/documentación/PRSC/Dailys.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="70">
   <si>
     <t xml:space="preserve">Daily</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t xml:space="preserve">Conexion supabe al proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar el funcionameinto de recuperar contraseña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E48" s="8" t="n">
         <v>8</v>
@@ -1922,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>8</v>
@@ -1938,15 +1944,27 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="B50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
+      <c r="J50" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="8"/>
